--- a/documents/Cases upload.xlsx
+++ b/documents/Cases upload.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darryllrobinson/Documents/projects/ciab/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962CE466-77DE-1F4F-8653-E9D4A96D4135}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F193FE-A064-6940-97E9-A9B3436EBC60}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="28380" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cases" sheetId="7" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cases!$A$1:$M$51</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -297,13 +300,13 @@
     <t>To be handed back to SADV. Do not action</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
     <t>OperatorShortCode</t>
   </si>
   <si>
     <t>SADV</t>
+  </si>
+  <si>
+    <t>Pended</t>
   </si>
 </sst>
 </file>
@@ -311,7 +314,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -389,10 +392,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -696,7 +699,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>71</v>
@@ -737,7 +740,7 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -764,12 +767,12 @@
         <v>81</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -796,12 +799,12 @@
         <v>81</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
@@ -828,7 +831,7 @@
         <v>81</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>68</v>
@@ -836,7 +839,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
@@ -863,7 +866,7 @@
         <v>81</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>53</v>
@@ -871,7 +874,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -898,12 +901,12 @@
         <v>81</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
@@ -930,12 +933,12 @@
         <v>81</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
@@ -962,12 +965,12 @@
         <v>81</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
@@ -994,7 +997,7 @@
         <v>81</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>70</v>
@@ -1002,7 +1005,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
@@ -1029,12 +1032,12 @@
         <v>81</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
@@ -1061,7 +1064,7 @@
         <v>81</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>51</v>
@@ -1069,7 +1072,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>11</v>
@@ -1104,7 +1107,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13" s="2">
         <v>12</v>
@@ -1131,12 +1134,12 @@
         <v>81</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B14" s="1">
         <v>13</v>
@@ -1171,7 +1174,7 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" s="2">
         <v>14</v>
@@ -1198,12 +1201,12 @@
         <v>81</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B16" s="2">
         <v>15</v>
@@ -1230,7 +1233,7 @@
         <v>81</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>60</v>
@@ -1238,7 +1241,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B17" s="1">
         <v>16</v>
@@ -1273,7 +1276,7 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B18" s="2">
         <v>17</v>
@@ -1300,12 +1303,12 @@
         <v>81</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B19" s="2">
         <v>18</v>
@@ -1332,12 +1335,12 @@
         <v>81</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" s="2">
         <v>19</v>
@@ -1364,12 +1367,12 @@
         <v>81</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="2">
         <v>20</v>
@@ -1396,12 +1399,12 @@
         <v>81</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B22" s="2">
         <v>21</v>
@@ -1428,12 +1431,12 @@
         <v>81</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2">
         <v>22</v>
@@ -1460,12 +1463,12 @@
         <v>81</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B24" s="2">
         <v>23</v>
@@ -1492,12 +1495,12 @@
         <v>81</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B25" s="2">
         <v>24</v>
@@ -1524,7 +1527,7 @@
         <v>81</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>63</v>
@@ -1532,7 +1535,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B26" s="2">
         <v>25</v>
@@ -1559,12 +1562,12 @@
         <v>81</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B27" s="2">
         <v>26</v>
@@ -1591,12 +1594,12 @@
         <v>81</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B28" s="2">
         <v>27</v>
@@ -1623,7 +1626,7 @@
         <v>81</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>69</v>
@@ -1631,7 +1634,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B29" s="2">
         <v>28</v>
@@ -1658,12 +1661,12 @@
         <v>81</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" s="2">
         <v>29</v>
@@ -1690,12 +1693,12 @@
         <v>81</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B31" s="2">
         <v>30</v>
@@ -1722,7 +1725,7 @@
         <v>81</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>56</v>
@@ -1730,7 +1733,7 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B32" s="2">
         <v>31</v>
@@ -1757,12 +1760,12 @@
         <v>81</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B33" s="2">
         <v>32</v>
@@ -1789,7 +1792,7 @@
         <v>81</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>59</v>
@@ -1797,7 +1800,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B34" s="2">
         <v>33</v>
@@ -1824,7 +1827,7 @@
         <v>81</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>65</v>
@@ -1832,7 +1835,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B35" s="2">
         <v>34</v>
@@ -1859,12 +1862,12 @@
         <v>81</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B36" s="2">
         <v>35</v>
@@ -1891,12 +1894,12 @@
         <v>81</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B37" s="2">
         <v>36</v>
@@ -1931,7 +1934,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B38" s="2">
         <v>37</v>
@@ -1958,7 +1961,7 @@
         <v>81</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>49</v>
@@ -1966,7 +1969,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B39" s="2">
         <v>38</v>
@@ -1993,7 +1996,7 @@
         <v>81</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>64</v>
@@ -2001,7 +2004,7 @@
     </row>
     <row r="40" spans="1:13" ht="43">
       <c r="A40" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B40" s="2">
         <v>39</v>
@@ -2028,7 +2031,7 @@
         <v>81</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>62</v>
@@ -2036,7 +2039,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B41" s="2">
         <v>40</v>
@@ -2063,12 +2066,12 @@
         <v>81</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B42" s="2">
         <v>41</v>
@@ -2095,7 +2098,7 @@
         <v>81</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>66</v>
@@ -2103,7 +2106,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B43" s="2">
         <v>42</v>
@@ -2130,12 +2133,12 @@
         <v>81</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B44" s="2">
         <v>43</v>
@@ -2162,12 +2165,12 @@
         <v>81</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B45" s="2">
         <v>44</v>
@@ -2194,7 +2197,7 @@
         <v>81</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>54</v>
@@ -2202,7 +2205,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B46" s="2">
         <v>45</v>
@@ -2229,12 +2232,12 @@
         <v>81</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B47" s="2">
         <v>46</v>
@@ -2261,7 +2264,7 @@
         <v>81</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>55</v>
@@ -2269,7 +2272,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B48" s="2">
         <v>47</v>
@@ -2296,12 +2299,12 @@
         <v>81</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B49" s="2">
         <v>48</v>
@@ -2328,12 +2331,12 @@
         <v>81</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B50" s="2">
         <v>49</v>
@@ -2360,12 +2363,12 @@
         <v>81</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B51" s="2">
         <v>50</v>
@@ -2392,7 +2395,7 @@
         <v>81</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/documents/Cases upload.xlsx
+++ b/documents/Cases upload.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darryllrobinson/Documents/projects/ciab/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F193FE-A064-6940-97E9-A9B3436EBC60}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C82DC8-CE5D-8849-923C-B75688D09EFA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="28380" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="89">
   <si>
     <t>3RD101</t>
   </si>
@@ -279,12 +279,6 @@
     <t>DateReopened</t>
   </si>
   <si>
-    <t>CaseReason</t>
-  </si>
-  <si>
-    <t>Account In Arrears</t>
-  </si>
-  <si>
     <t>CaseNotes</t>
   </si>
   <si>
@@ -307,14 +301,18 @@
   </si>
   <si>
     <t>Pended</t>
+  </si>
+  <si>
+    <t>nextVisitDateTime</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -374,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -398,6 +396,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -679,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96F675B-1693-41B7-959B-84DE2013B8DF}">
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M596"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
@@ -692,14 +697,14 @@
     <col min="8" max="8" width="18.5" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="146" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>71</v>
@@ -728,19 +733,19 @@
       <c r="J1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -763,16 +768,16 @@
       <c r="H2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>81</v>
+      <c r="K2" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -795,16 +800,16 @@
       <c r="H3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>81</v>
+      <c r="K3" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2">
         <v>3</v>
@@ -827,11 +832,11 @@
       <c r="H4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>81</v>
+      <c r="K4" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>68</v>
@@ -839,7 +844,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
@@ -862,11 +867,11 @@
       <c r="H5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>81</v>
+      <c r="K5" s="13">
+        <v>44040.375</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>53</v>
@@ -874,7 +879,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -897,16 +902,16 @@
       <c r="H6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>81</v>
+      <c r="K6" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B7" s="2">
         <v>6</v>
@@ -929,16 +934,16 @@
       <c r="H7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>81</v>
+      <c r="K7" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2">
         <v>7</v>
@@ -961,16 +966,16 @@
       <c r="H8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>81</v>
+      <c r="K8" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B9" s="2">
         <v>8</v>
@@ -993,11 +998,11 @@
       <c r="H9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>81</v>
+      <c r="K9" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>70</v>
@@ -1005,7 +1010,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
@@ -1028,16 +1033,16 @@
       <c r="H10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>81</v>
+      <c r="K10" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
@@ -1060,11 +1065,11 @@
       <c r="H11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>81</v>
+      <c r="K11" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>51</v>
@@ -1072,7 +1077,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B12" s="1">
         <v>11</v>
@@ -1095,11 +1100,11 @@
       <c r="H12" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>81</v>
+      <c r="K12" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>67</v>
@@ -1107,7 +1112,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B13" s="2">
         <v>12</v>
@@ -1130,16 +1135,16 @@
       <c r="H13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>81</v>
+      <c r="K13" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B14" s="1">
         <v>13</v>
@@ -1162,11 +1167,11 @@
       <c r="H14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>81</v>
+      <c r="K14" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>52</v>
@@ -1174,7 +1179,7 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B15" s="2">
         <v>14</v>
@@ -1197,16 +1202,16 @@
       <c r="H15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>81</v>
+      <c r="K15" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B16" s="2">
         <v>15</v>
@@ -1229,11 +1234,11 @@
       <c r="H16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>81</v>
+      <c r="K16" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>60</v>
@@ -1241,7 +1246,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B17" s="1">
         <v>16</v>
@@ -1264,11 +1269,11 @@
       <c r="H17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>81</v>
+      <c r="K17" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M17" s="5" t="s">
         <v>61</v>
@@ -1276,7 +1281,7 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B18" s="2">
         <v>17</v>
@@ -1299,16 +1304,16 @@
       <c r="H18" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>81</v>
+      <c r="K18" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2">
         <v>18</v>
@@ -1331,16 +1336,16 @@
       <c r="H19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>81</v>
+      <c r="K19" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2">
         <v>19</v>
@@ -1363,16 +1368,16 @@
       <c r="H20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>81</v>
+      <c r="K20" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B21" s="2">
         <v>20</v>
@@ -1395,16 +1400,16 @@
       <c r="H21" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>81</v>
+      <c r="K21" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2">
         <v>21</v>
@@ -1427,16 +1432,16 @@
       <c r="H22" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>81</v>
+      <c r="K22" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B23" s="2">
         <v>22</v>
@@ -1459,16 +1464,16 @@
       <c r="H23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>81</v>
+      <c r="K23" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B24" s="2">
         <v>23</v>
@@ -1491,16 +1496,16 @@
       <c r="H24" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>81</v>
+      <c r="K24" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B25" s="2">
         <v>24</v>
@@ -1523,11 +1528,11 @@
       <c r="H25" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>81</v>
+      <c r="K25" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>63</v>
@@ -1535,7 +1540,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B26" s="2">
         <v>25</v>
@@ -1558,16 +1563,16 @@
       <c r="H26" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>81</v>
+      <c r="K26" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B27" s="2">
         <v>26</v>
@@ -1590,16 +1595,16 @@
       <c r="H27" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>81</v>
+      <c r="K27" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B28" s="2">
         <v>27</v>
@@ -1622,11 +1627,11 @@
       <c r="H28" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>81</v>
+      <c r="K28" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>69</v>
@@ -1634,7 +1639,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B29" s="2">
         <v>28</v>
@@ -1657,16 +1662,16 @@
       <c r="H29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>81</v>
+      <c r="K29" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B30" s="2">
         <v>29</v>
@@ -1689,16 +1694,16 @@
       <c r="H30" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>81</v>
+      <c r="K30" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B31" s="2">
         <v>30</v>
@@ -1721,11 +1726,11 @@
       <c r="H31" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>81</v>
+      <c r="K31" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>56</v>
@@ -1733,7 +1738,7 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B32" s="2">
         <v>31</v>
@@ -1756,16 +1761,16 @@
       <c r="H32" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>81</v>
+      <c r="K32" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B33" s="2">
         <v>32</v>
@@ -1788,11 +1793,11 @@
       <c r="H33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>81</v>
+      <c r="K33" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>59</v>
@@ -1800,7 +1805,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B34" s="2">
         <v>33</v>
@@ -1823,11 +1828,11 @@
       <c r="H34" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>81</v>
+      <c r="K34" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>65</v>
@@ -1835,7 +1840,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B35" s="2">
         <v>34</v>
@@ -1858,16 +1863,16 @@
       <c r="H35" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>81</v>
+      <c r="K35" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B36" s="2">
         <v>35</v>
@@ -1890,16 +1895,16 @@
       <c r="H36" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>81</v>
+      <c r="K36" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B37" s="2">
         <v>36</v>
@@ -1922,19 +1927,19 @@
       <c r="H37" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>81</v>
+      <c r="K37" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B38" s="2">
         <v>37</v>
@@ -1957,11 +1962,11 @@
       <c r="H38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>81</v>
+      <c r="K38" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>49</v>
@@ -1969,7 +1974,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B39" s="2">
         <v>38</v>
@@ -1992,11 +1997,11 @@
       <c r="H39" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>81</v>
+      <c r="K39" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>64</v>
@@ -2004,7 +2009,7 @@
     </row>
     <row r="40" spans="1:13" ht="43">
       <c r="A40" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B40" s="2">
         <v>39</v>
@@ -2027,11 +2032,11 @@
       <c r="H40" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>81</v>
+      <c r="K40" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>62</v>
@@ -2039,7 +2044,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B41" s="2">
         <v>40</v>
@@ -2062,16 +2067,16 @@
       <c r="H41" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K41" s="2" t="s">
-        <v>81</v>
+      <c r="K41" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B42" s="2">
         <v>41</v>
@@ -2094,11 +2099,11 @@
       <c r="H42" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K42" s="2" t="s">
-        <v>81</v>
+      <c r="K42" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>66</v>
@@ -2106,7 +2111,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B43" s="2">
         <v>42</v>
@@ -2129,16 +2134,16 @@
       <c r="H43" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K43" s="2" t="s">
-        <v>81</v>
+      <c r="K43" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B44" s="2">
         <v>43</v>
@@ -2161,16 +2166,16 @@
       <c r="H44" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>81</v>
+      <c r="K44" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B45" s="2">
         <v>44</v>
@@ -2193,11 +2198,11 @@
       <c r="H45" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K45" s="2" t="s">
-        <v>81</v>
+      <c r="K45" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>54</v>
@@ -2205,7 +2210,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B46" s="2">
         <v>45</v>
@@ -2228,16 +2233,16 @@
       <c r="H46" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K46" s="2" t="s">
-        <v>81</v>
+      <c r="K46" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B47" s="2">
         <v>46</v>
@@ -2260,11 +2265,11 @@
       <c r="H47" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K47" s="2" t="s">
-        <v>81</v>
+      <c r="K47" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>55</v>
@@ -2272,7 +2277,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B48" s="2">
         <v>47</v>
@@ -2295,16 +2300,16 @@
       <c r="H48" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K48" s="2" t="s">
-        <v>81</v>
+      <c r="K48" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B49" s="2">
         <v>48</v>
@@ -2327,16 +2332,16 @@
       <c r="H49" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K49" s="2" t="s">
-        <v>81</v>
+      <c r="K49" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B50" s="2">
         <v>49</v>
@@ -2359,16 +2364,16 @@
       <c r="H50" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>81</v>
+      <c r="K50" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B51" s="2">
         <v>50</v>
@@ -2391,12 +2396,477 @@
       <c r="H51" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K51" s="2" t="s">
-        <v>81</v>
+      <c r="K51" s="13">
+        <v>44048.375</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>89</v>
-      </c>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="K52" s="13"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="K53" s="13"/>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="K54" s="13"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="K55" s="13"/>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="K56" s="13"/>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="K57" s="13"/>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="K58" s="13"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="K59" s="13"/>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="K60" s="13"/>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="K61" s="13"/>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="K62" s="13"/>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="K63" s="12"/>
+    </row>
+    <row r="65" spans="11:11">
+      <c r="K65" s="12"/>
+    </row>
+    <row r="66" spans="11:11">
+      <c r="K66" s="12"/>
+    </row>
+    <row r="67" spans="11:11">
+      <c r="K67" s="12"/>
+    </row>
+    <row r="457" spans="11:11">
+      <c r="K457" s="11"/>
+    </row>
+    <row r="458" spans="11:11">
+      <c r="K458" s="11"/>
+    </row>
+    <row r="459" spans="11:11">
+      <c r="K459" s="11"/>
+    </row>
+    <row r="460" spans="11:11">
+      <c r="K460" s="11"/>
+    </row>
+    <row r="461" spans="11:11">
+      <c r="K461" s="11"/>
+    </row>
+    <row r="462" spans="11:11">
+      <c r="K462" s="11"/>
+    </row>
+    <row r="463" spans="11:11">
+      <c r="K463" s="11"/>
+    </row>
+    <row r="464" spans="11:11">
+      <c r="K464" s="11"/>
+    </row>
+    <row r="465" spans="11:11">
+      <c r="K465" s="11"/>
+    </row>
+    <row r="466" spans="11:11">
+      <c r="K466" s="11"/>
+    </row>
+    <row r="467" spans="11:11">
+      <c r="K467" s="11"/>
+    </row>
+    <row r="468" spans="11:11">
+      <c r="K468" s="11"/>
+    </row>
+    <row r="469" spans="11:11">
+      <c r="K469" s="11"/>
+    </row>
+    <row r="470" spans="11:11">
+      <c r="K470" s="11"/>
+    </row>
+    <row r="471" spans="11:11">
+      <c r="K471" s="11"/>
+    </row>
+    <row r="472" spans="11:11">
+      <c r="K472" s="11"/>
+    </row>
+    <row r="473" spans="11:11">
+      <c r="K473" s="11"/>
+    </row>
+    <row r="474" spans="11:11">
+      <c r="K474" s="11"/>
+    </row>
+    <row r="475" spans="11:11">
+      <c r="K475" s="11"/>
+    </row>
+    <row r="476" spans="11:11">
+      <c r="K476" s="11"/>
+    </row>
+    <row r="477" spans="11:11">
+      <c r="K477" s="11"/>
+    </row>
+    <row r="478" spans="11:11">
+      <c r="K478" s="11"/>
+    </row>
+    <row r="479" spans="11:11">
+      <c r="K479" s="11"/>
+    </row>
+    <row r="480" spans="11:11">
+      <c r="K480" s="11"/>
+    </row>
+    <row r="481" spans="11:11">
+      <c r="K481" s="11"/>
+    </row>
+    <row r="482" spans="11:11">
+      <c r="K482" s="11"/>
+    </row>
+    <row r="483" spans="11:11">
+      <c r="K483" s="11"/>
+    </row>
+    <row r="484" spans="11:11">
+      <c r="K484" s="11"/>
+    </row>
+    <row r="485" spans="11:11">
+      <c r="K485" s="11"/>
+    </row>
+    <row r="486" spans="11:11">
+      <c r="K486" s="11"/>
+    </row>
+    <row r="487" spans="11:11">
+      <c r="K487" s="11"/>
+    </row>
+    <row r="488" spans="11:11">
+      <c r="K488" s="11"/>
+    </row>
+    <row r="489" spans="11:11">
+      <c r="K489" s="11"/>
+    </row>
+    <row r="490" spans="11:11">
+      <c r="K490" s="11"/>
+    </row>
+    <row r="491" spans="11:11">
+      <c r="K491" s="11"/>
+    </row>
+    <row r="492" spans="11:11">
+      <c r="K492" s="11"/>
+    </row>
+    <row r="493" spans="11:11">
+      <c r="K493" s="11"/>
+    </row>
+    <row r="494" spans="11:11">
+      <c r="K494" s="11"/>
+    </row>
+    <row r="495" spans="11:11">
+      <c r="K495" s="11"/>
+    </row>
+    <row r="496" spans="11:11">
+      <c r="K496" s="11"/>
+    </row>
+    <row r="497" spans="11:11">
+      <c r="K497" s="11"/>
+    </row>
+    <row r="498" spans="11:11">
+      <c r="K498" s="11"/>
+    </row>
+    <row r="499" spans="11:11">
+      <c r="K499" s="11"/>
+    </row>
+    <row r="500" spans="11:11">
+      <c r="K500" s="11"/>
+    </row>
+    <row r="501" spans="11:11">
+      <c r="K501" s="11"/>
+    </row>
+    <row r="502" spans="11:11">
+      <c r="K502" s="11"/>
+    </row>
+    <row r="503" spans="11:11">
+      <c r="K503" s="11"/>
+    </row>
+    <row r="504" spans="11:11">
+      <c r="K504" s="11"/>
+    </row>
+    <row r="505" spans="11:11">
+      <c r="K505" s="11"/>
+    </row>
+    <row r="506" spans="11:11">
+      <c r="K506" s="11"/>
+    </row>
+    <row r="507" spans="11:11">
+      <c r="K507" s="11"/>
+    </row>
+    <row r="508" spans="11:11">
+      <c r="K508" s="11"/>
+    </row>
+    <row r="509" spans="11:11">
+      <c r="K509" s="11"/>
+    </row>
+    <row r="510" spans="11:11">
+      <c r="K510" s="11"/>
+    </row>
+    <row r="511" spans="11:11">
+      <c r="K511" s="11"/>
+    </row>
+    <row r="512" spans="11:11">
+      <c r="K512" s="11"/>
+    </row>
+    <row r="513" spans="11:11">
+      <c r="K513" s="11"/>
+    </row>
+    <row r="514" spans="11:11">
+      <c r="K514" s="11"/>
+    </row>
+    <row r="515" spans="11:11">
+      <c r="K515" s="11"/>
+    </row>
+    <row r="516" spans="11:11">
+      <c r="K516" s="11"/>
+    </row>
+    <row r="517" spans="11:11">
+      <c r="K517" s="11"/>
+    </row>
+    <row r="518" spans="11:11">
+      <c r="K518" s="11"/>
+    </row>
+    <row r="519" spans="11:11">
+      <c r="K519" s="11"/>
+    </row>
+    <row r="520" spans="11:11">
+      <c r="K520" s="11"/>
+    </row>
+    <row r="521" spans="11:11">
+      <c r="K521" s="11"/>
+    </row>
+    <row r="522" spans="11:11">
+      <c r="K522" s="11"/>
+    </row>
+    <row r="523" spans="11:11">
+      <c r="K523" s="11"/>
+    </row>
+    <row r="524" spans="11:11">
+      <c r="K524" s="11"/>
+    </row>
+    <row r="525" spans="11:11">
+      <c r="K525" s="11"/>
+    </row>
+    <row r="526" spans="11:11">
+      <c r="K526" s="11"/>
+    </row>
+    <row r="527" spans="11:11">
+      <c r="K527" s="11"/>
+    </row>
+    <row r="528" spans="11:11">
+      <c r="K528" s="11"/>
+    </row>
+    <row r="529" spans="11:11">
+      <c r="K529" s="11"/>
+    </row>
+    <row r="530" spans="11:11">
+      <c r="K530" s="11"/>
+    </row>
+    <row r="531" spans="11:11">
+      <c r="K531" s="11"/>
+    </row>
+    <row r="532" spans="11:11">
+      <c r="K532" s="11"/>
+    </row>
+    <row r="533" spans="11:11">
+      <c r="K533" s="11"/>
+    </row>
+    <row r="534" spans="11:11">
+      <c r="K534" s="11"/>
+    </row>
+    <row r="535" spans="11:11">
+      <c r="K535" s="11"/>
+    </row>
+    <row r="536" spans="11:11">
+      <c r="K536" s="11"/>
+    </row>
+    <row r="537" spans="11:11">
+      <c r="K537" s="11"/>
+    </row>
+    <row r="538" spans="11:11">
+      <c r="K538" s="11"/>
+    </row>
+    <row r="539" spans="11:11">
+      <c r="K539" s="11"/>
+    </row>
+    <row r="540" spans="11:11">
+      <c r="K540" s="11"/>
+    </row>
+    <row r="541" spans="11:11">
+      <c r="K541" s="11"/>
+    </row>
+    <row r="542" spans="11:11">
+      <c r="K542" s="11"/>
+    </row>
+    <row r="543" spans="11:11">
+      <c r="K543" s="11"/>
+    </row>
+    <row r="544" spans="11:11">
+      <c r="K544" s="11"/>
+    </row>
+    <row r="545" spans="11:11">
+      <c r="K545" s="11"/>
+    </row>
+    <row r="546" spans="11:11">
+      <c r="K546" s="11"/>
+    </row>
+    <row r="547" spans="11:11">
+      <c r="K547" s="11"/>
+    </row>
+    <row r="548" spans="11:11">
+      <c r="K548" s="11"/>
+    </row>
+    <row r="549" spans="11:11">
+      <c r="K549" s="11"/>
+    </row>
+    <row r="550" spans="11:11">
+      <c r="K550" s="11"/>
+    </row>
+    <row r="551" spans="11:11">
+      <c r="K551" s="11"/>
+    </row>
+    <row r="552" spans="11:11">
+      <c r="K552" s="11"/>
+    </row>
+    <row r="553" spans="11:11">
+      <c r="K553" s="11"/>
+    </row>
+    <row r="554" spans="11:11">
+      <c r="K554" s="11"/>
+    </row>
+    <row r="555" spans="11:11">
+      <c r="K555" s="11"/>
+    </row>
+    <row r="556" spans="11:11">
+      <c r="K556" s="11"/>
+    </row>
+    <row r="557" spans="11:11">
+      <c r="K557" s="11"/>
+    </row>
+    <row r="558" spans="11:11">
+      <c r="K558" s="11"/>
+    </row>
+    <row r="559" spans="11:11">
+      <c r="K559" s="11"/>
+    </row>
+    <row r="560" spans="11:11">
+      <c r="K560" s="11"/>
+    </row>
+    <row r="561" spans="11:11">
+      <c r="K561" s="11"/>
+    </row>
+    <row r="562" spans="11:11">
+      <c r="K562" s="11"/>
+    </row>
+    <row r="563" spans="11:11">
+      <c r="K563" s="11"/>
+    </row>
+    <row r="564" spans="11:11">
+      <c r="K564" s="11"/>
+    </row>
+    <row r="565" spans="11:11">
+      <c r="K565" s="11"/>
+    </row>
+    <row r="566" spans="11:11">
+      <c r="K566" s="11"/>
+    </row>
+    <row r="567" spans="11:11">
+      <c r="K567" s="11"/>
+    </row>
+    <row r="568" spans="11:11">
+      <c r="K568" s="11"/>
+    </row>
+    <row r="569" spans="11:11">
+      <c r="K569" s="11"/>
+    </row>
+    <row r="570" spans="11:11">
+      <c r="K570" s="11"/>
+    </row>
+    <row r="571" spans="11:11">
+      <c r="K571" s="11"/>
+    </row>
+    <row r="572" spans="11:11">
+      <c r="K572" s="11"/>
+    </row>
+    <row r="573" spans="11:11">
+      <c r="K573" s="11"/>
+    </row>
+    <row r="574" spans="11:11">
+      <c r="K574" s="11"/>
+    </row>
+    <row r="575" spans="11:11">
+      <c r="K575" s="11"/>
+    </row>
+    <row r="576" spans="11:11">
+      <c r="K576" s="11"/>
+    </row>
+    <row r="577" spans="11:11">
+      <c r="K577" s="11"/>
+    </row>
+    <row r="578" spans="11:11">
+      <c r="K578" s="11"/>
+    </row>
+    <row r="579" spans="11:11">
+      <c r="K579" s="11"/>
+    </row>
+    <row r="580" spans="11:11">
+      <c r="K580" s="11"/>
+    </row>
+    <row r="581" spans="11:11">
+      <c r="K581" s="11"/>
+    </row>
+    <row r="582" spans="11:11">
+      <c r="K582" s="11"/>
+    </row>
+    <row r="583" spans="11:11">
+      <c r="K583" s="11"/>
+    </row>
+    <row r="584" spans="11:11">
+      <c r="K584" s="11"/>
+    </row>
+    <row r="585" spans="11:11">
+      <c r="K585" s="11"/>
+    </row>
+    <row r="586" spans="11:11">
+      <c r="K586" s="11"/>
+    </row>
+    <row r="587" spans="11:11">
+      <c r="K587" s="11"/>
+    </row>
+    <row r="588" spans="11:11">
+      <c r="K588" s="11"/>
+    </row>
+    <row r="589" spans="11:11">
+      <c r="K589" s="11"/>
+    </row>
+    <row r="590" spans="11:11">
+      <c r="K590" s="11"/>
+    </row>
+    <row r="591" spans="11:11">
+      <c r="K591" s="11"/>
+    </row>
+    <row r="592" spans="11:11">
+      <c r="K592" s="11"/>
+    </row>
+    <row r="593" spans="11:11">
+      <c r="K593" s="11"/>
+    </row>
+    <row r="594" spans="11:11">
+      <c r="K594" s="11"/>
+    </row>
+    <row r="595" spans="11:11">
+      <c r="K595" s="11"/>
+    </row>
+    <row r="596" spans="11:11">
+      <c r="K596" s="11"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:N51">
